--- a/02_DIA_inicio_2026_analisis_assets/rbd_9458_escuela-boroa_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9458_escuela-boroa_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D2C7CF-ECE7-4CD9-9AAB-5DEBB8C10AB8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADCA3D5D-58C8-4046-8441-D468CFCD9BBF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30C20D11-74D1-40C6-9288-40977ABB594B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2804E6DD-85A5-4A01-A8F0-4E7F555FCC06}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F60EF61C-EF98-4CEB-BB81-B49B229E06F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AD86BA4-B6A2-480C-ACE4-EF45F2A09A3E}"/>
 </file>